--- a/docs/reports/portfolio-api-economics-register-stage2-2026-09-02.xlsx
+++ b/docs/reports/portfolio-api-economics-register-stage2-2026-09-02.xlsx
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI23"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3018,9 +3018,9 @@
           <t>MATERIAL for TI's weather feature; N/A for Corralio (not built)</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>AUDIT</t>
+      <c r="AA14" s="11" t="inlineStr">
+        <is>
+          <t>SWAP / RETIRE</t>
         </is>
       </c>
       <c r="AB14" s="9" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>Whether a commercial Open-Meteo license already exists outside the repository (see Section 2 verdict)</t>
+          <t>Whether a commercial Open-Meteo license already exists outside the repository (see Section 2 verdict) -- Superseded 2026-09-02: founder decided to swap to WeatherAPI.com rather than resolve licensing ambiguity, sidestepping the open question entirely rather than answering it.</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="AH14" s="7" t="inlineStr">
         <is>
-          <t>Section 3 verdict this pass: UNRESOLVED -- FOUNDER ACTION REQUIRED (see report). Repo evidence (free tier's own non-commercial restriction, internal FREE_TIER_LIMITS table labeling it 'Free (non-commercial)', no billing artifact anywhere in repo) points toward no commercial plan, but confirming the account/billing state itself is outside what this session can see.</t>
+          <t>Section 3 verdict this pass: UNRESOLVED -- FOUNDER ACTION REQUIRED (see report). Repo evidence (free tier's own non-commercial restriction, internal FREE_TIER_LIMITS table labeling it 'Free (non-commercial)', no billing artifact anywhere in repo) points toward no commercial plan, but confirming the account/billing state itself is outside what this session can see. STAGE 3 UPDATE (2026-09-02): founder decision is to retire Open-Meteo rather than resolve its licensing status -- see WeatherAPI.com row. Retire only after the migration below is verified in production; do not remove the Open-Meteo call sites before WeatherAPI.com is confirmed serving equivalent or better data in the same UI contract.</t>
         </is>
       </c>
       <c r="AI14" s="7" t="inlineStr">
         <is>
-          <t>Founder confirms via Open-Meteo account/billing records (or a direct email to Open-Meteo) whether a commercial arrangement already exists. See Section 3.</t>
+          <t>Execute the implementation design + migration prompt (docs/prompts/2026-09-02-weatherapi-migration-implementation-prompt.md). Retire Open-Meteo call sites + enum entry only after production verification.</t>
         </is>
       </c>
     </row>
@@ -4654,6 +4654,183 @@
       <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>Founder/ops env-var confirmation; no implementation authorized here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>WeatherAPI.com</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>TI + Corralio initially; RI when useful for the venue/travel experience (founder decision, 2026-09-02)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Not yet -- design/migration prompt filed 2026-09-02, not implemented</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: replaces apps/ti-web/app/api/weather/ten-day/route.ts; new Corralio event-aware weather surface; shared persistent cache layer serving all three products</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>PASSIVE_RENDER (same as Open-Meteo today) + new Corralio event-aware trigger (TBD in migration design)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Yes (same as today, cache-miss path only once shared cache lands)</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Same shape as Open-Meteo today -- mitigated by the shared persistent cache from day one, not added after the fact</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: shared persistent venue/grid-keyed cache (per Section 4 of the 2026-09-02 Stage 2 report), not the time-based-only pattern Open-Meteo used</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TBD in migration design -- deterministic freshness window (hours, not the prior 30-minute time-based-only TTL)</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: yes, from initial build -- corrects Open-Meteo's biggest architectural gap (no DB-backed cache ever existed)</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>PORTFOLIO -- one cache serving TI + Corralio + (later) RI, by design</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: wrapped in trackExternalCall() from day one (server-only credentials + usage tracking, per the founder's own stated sequence) -- corrects Open-Meteo's confirmed instrumentation gap</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>100K calls/month free tier, commercial use explicitly permitted (verified live 2026-09-02, weatherapi.com/pricing.aspx: "Commercial Use: Yes - permitted on the free plan") -- this is the fact that resolves the exact compliance question Open-Meteo left unresolved</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Starter $7/mo for 3M calls (verified live 2026-09-02) -- cheaper per-call headroom than Open-Meteo's paid tier (~$29/mo for 1M) if usage ever exceeds the free 100K/month</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>100K calls/mo free; 3M/5M/10M on Starter $7 / Pro+ $25 / Business $65 monthly plans (verified live 2026-09-02)</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>$0 (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>$0 (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>N/A (paid/freemium provider, not open data)</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>YES -- this IS the shared-data build, by design, per the founder's stated sequence (shared cache before Corralio/RI expansion)</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>Planning intelligence (founder's label) -- maps to CORE_PRODUCT for TI's existing weather feature and DIFFERENTIATION for Corralio's weekend-forecast value proposition</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>MATERIAL once live -- same as Open-Meteo's current role, intentionally no functional regression during the swap</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="inlineStr">
+        <is>
+          <t>KEEP / SHARED CORE PRODUCT</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>No production usage yet -- this is a pre-implementation register entry. Free-tier 100K/month ceiling is meaningfully lower than Open-Meteo's 300K/month -- worth watching once the shared cache is live, since the cache design should collapse raw call volume well below either ceiling, but this hasn't been measured yet because nothing has been built.</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>Verified live 2026-09-02: weatherapi.com/pricing.aspx (plan pricing, commercial-use permission) and weatherapi.com/docs/ (hourly support, 14-day horizon, alerts=yes parameter, query-param API key auth)</t>
+        </is>
+      </c>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>N/A -- not yet implemented</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>N/A -- pre-implementation, pricing/terms verified live, not a usage measurement</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>HIGH on pricing/terms/capability (verified live 2026-09-02); N/A on usage (not yet built)</t>
+        </is>
+      </c>
+      <c r="AH24" s="7" t="inlineStr">
+        <is>
+          <t>See rationale field.</t>
+        </is>
+      </c>
+      <c r="AI24" s="7" t="inlineStr">
+        <is>
+          <t>See next_test field.</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5813,7 +5990,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Whether a commercial Open-Meteo license already exists outside the repository (see Section 2 verdict)</t>
+          <t>Whether a commercial Open-Meteo license already exists outside the repository (see Section 2 verdict) -- Superseded 2026-09-02: founder decided to swap to WeatherAPI.com rather than resolve licensing ambiguity, sidestepping the open question entirely rather than answering it.</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -5833,7 +6010,7 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>Founder confirms via Open-Meteo account/billing records (or a direct email to Open-Meteo) whether a commercial arrangement already exists. See Section 3.</t>
+          <t>Execute the implementation design + migration prompt (docs/prompts/2026-09-02-weatherapi-migration-implementation-prompt.md). Retire Open-Meteo call sites + enum entry only after production verification.</t>
         </is>
       </c>
     </row>
@@ -6572,6 +6749,88 @@
       <c r="P23" s="7" t="inlineStr">
         <is>
           <t>Founder/ops env-var confirmation; no implementation authorized here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>WeatherAPI.com</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>100K calls/month free tier, commercial use explicitly permitted (verified live 2026-09-02, weatherapi.com/pricing.aspx: "Commercial Use: Yes - permitted on the free plan") -- this is the fact that resolves the exact compliance question Open-Meteo left unresolved</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Starter $7/mo for 3M calls (verified live 2026-09-02) -- cheaper per-call headroom than Open-Meteo's paid tier (~$29/mo for 1M) if usage ever exceeds the free 100K/month</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>100K calls/mo free; 3M/5M/10M on Starter $7 / Pro+ $25 / Business $65 monthly plans (verified live 2026-09-02)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>$0 (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>$0 (not yet implemented)</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>No production usage yet -- this is a pre-implementation register entry. Free-tier 100K/month ceiling is meaningfully lower than Open-Meteo's 300K/month -- worth watching once the shared cache is live, since the cache design should collapse raw call volume well below either ceiling, but this hasn't been measured yet because nothing has been built.</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Verified live 2026-09-02: weatherapi.com/pricing.aspx (plan pricing, commercial-use permission) and weatherapi.com/docs/ (hourly support, 14-day horizon, alerts=yes parameter, query-param API key auth)</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>N/A -- not yet implemented</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>N/A -- pre-implementation, pricing/terms verified live, not a usage measurement</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>See next_test field.</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8145,6 +8404,73 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>WeatherAPI.com</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: replaces apps/ti-web/app/api/weather/ten-day/route.ts; new Corralio event-aware weather surface; shared persistent cache layer serving all three products</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>PASSIVE_RENDER (same as Open-Meteo today) + new Corralio event-aware trigger (TBD in migration design)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Yes (same as today, cache-miss path only once shared cache lands)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Same shape as Open-Meteo today -- mitigated by the shared persistent cache from day one, not added after the fact</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: shared persistent venue/grid-keyed cache (per Section 4 of the 2026-09-02 Stage 2 report), not the time-based-only pattern Open-Meteo used</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>TBD in migration design -- deterministic freshness window (hours, not the prior 30-minute time-based-only TTL)</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: yes, from initial build -- corrects Open-Meteo's biggest architectural gap (no DB-backed cache ever existed)</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>PORTFOLIO -- one cache serving TI + Corralio + (later) RI, by design</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Planning intelligence (founder's label) -- maps to CORE_PRODUCT for TI's existing weather feature and DIFFERENTIATION for Corralio's weekend-forecast value proposition</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>MATERIAL once live -- same as Open-Meteo's current role, intentionally no functional regression during the swap</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8156,7 +8482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8807,9 +9133,9 @@
           <t>YES — the cleanest shared-data case in the register; one venue/grid-keyed forecast cache could serve TI+RI+Corralio, since weather has no product-specific ownership</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>AUDIT</t>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>SWAP / RETIRE</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -8819,12 +9145,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Section 3 verdict this pass: UNRESOLVED -- FOUNDER ACTION REQUIRED (see report). Repo evidence (free tier's own non-commercial restriction, internal FREE_TIER_LIMITS table labeling it 'Free (non-commercial)', no billing artifact anywhere in repo) points toward no commercial plan, but confirming the account/billing state itself is outside what this session can see.</t>
+          <t>Section 3 verdict this pass: UNRESOLVED -- FOUNDER ACTION REQUIRED (see report). Repo evidence (free tier's own non-commercial restriction, internal FREE_TIER_LIMITS table labeling it 'Free (non-commercial)', no billing artifact anywhere in repo) points toward no commercial plan, but confirming the account/billing state itself is outside what this session can see. STAGE 3 UPDATE (2026-09-02): founder decision is to retire Open-Meteo rather than resolve its licensing status -- see WeatherAPI.com row. Retire only after the migration below is verified in production; do not remove the Open-Meteo call sites before WeatherAPI.com is confirmed serving equivalent or better data in the same UI contract.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Founder confirms via Open-Meteo account/billing records (or a direct email to Open-Meteo) whether a commercial arrangement already exists. See Section 3.</t>
+          <t>Execute the implementation design + migration prompt (docs/prompts/2026-09-02-weatherapi-migration-implementation-prompt.md). Retire Open-Meteo call sites + enum entry only after production verification.</t>
         </is>
       </c>
     </row>
@@ -9248,6 +9574,53 @@
       <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Founder/ops env-var confirmation; no implementation authorized here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>WeatherAPI.com</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Planned: replaces apps/ti-web/app/api/weather/ten-day/route.ts; new Corralio event-aware weather surface; shared persistent cache layer serving all three products</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>N/A (paid/freemium provider, not open data)</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>YES -- this IS the shared-data build, by design, per the founder's stated sequence (shared cache before Corralio/RI expansion)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>KEEP / SHARED CORE PRODUCT</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>See rationale field.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>See next_test field.</t>
         </is>
       </c>
     </row>

--- a/docs/reports/portfolio-api-economics-register-stage2-2026-09-02.xlsx
+++ b/docs/reports/portfolio-api-economics-register-stage2-2026-09-02.xlsx
@@ -4665,12 +4665,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+          <t>Weather forecast (daily + hourly) + severe weather alerts capability (unused), replacing Open-Meteo -- one shared client for TI + Corralio, Corralio shipped in the same build cycle (founder correction 2026-09-02)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>TI + Corralio initially; RI when useful for the venue/travel experience (founder decision, 2026-09-02)</t>
+          <t>TI + Corralio, same build cycle (founder correction 2026-09-02: Corralio weather is core product value, not deferred infrastructure); RI when a specific surface is justified</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -4700,22 +4700,22 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Planned: shared persistent venue/grid-keyed cache (per Section 4 of the 2026-09-02 Stage 2 report), not the time-based-only pattern Open-Meteo used</t>
+          <t>Shared server client applies ordinary Next.js fetch-revalidate / CDN Cache-Control (30-min-class TTL, matching TI current pattern) -- NOT a persistent DB cache initially, per founder correction 2026-09-02 (measure real volume/cost before building schema+migrations to optimize a $7/mo bill)</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>TBD in migration design -- deterministic freshness window (hours, not the prior 30-minute time-based-only TTL)</t>
+          <t>~30 min (Next/CDN), matching TI current pattern; re-evaluated only if Phase 5 (persistent cache) is triggered</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Planned: yes, from initial build -- corrects Open-Meteo's biggest architectural gap (no DB-backed cache ever existed)</t>
+          <t>No, initially -- deferred to Phase 5, built only if 30-day production measurement (Phase 4) shows call volume/latency/error evidence that justifies it. Client is designed so a cache can be inserted later without changing callers.</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>PORTFOLIO -- one cache serving TI + Corralio + (later) RI, by design</t>
+          <t>One shared server module/client used by TI + Corralio (+ RI later) -- portfolio-wide at the INTEGRATION level from day one; response-data reuse across apps is deferred to Phase 5, not assumed from the start</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="AH24" s="7" t="inlineStr">
         <is>
-          <t>See rationale field.</t>
+          <t>REVISED 2026-09-02: see rationale field. Register updated in place per this session convention.</t>
         </is>
       </c>
       <c r="AI24" s="7" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+          <t>Weather forecast (daily + hourly) + severe weather alerts capability (unused), replacing Open-Meteo -- one shared client for TI + Corralio, Corralio shipped in the same build cycle (founder correction 2026-09-02)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+          <t>Weather forecast (daily + hourly) + severe weather alerts capability (unused), replacing Open-Meteo -- one shared client for TI + Corralio, Corralio shipped in the same build cycle (founder correction 2026-09-02)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -8437,22 +8437,22 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Planned: shared persistent venue/grid-keyed cache (per Section 4 of the 2026-09-02 Stage 2 report), not the time-based-only pattern Open-Meteo used</t>
+          <t>Shared server client applies ordinary Next.js fetch-revalidate / CDN Cache-Control (30-min-class TTL, matching TI current pattern) -- NOT a persistent DB cache initially, per founder correction 2026-09-02 (measure real volume/cost before building schema+migrations to optimize a $7/mo bill)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>TBD in migration design -- deterministic freshness window (hours, not the prior 30-minute time-based-only TTL)</t>
+          <t>~30 min (Next/CDN), matching TI current pattern; re-evaluated only if Phase 5 (persistent cache) is triggered</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Planned: yes, from initial build -- corrects Open-Meteo's biggest architectural gap (no DB-backed cache ever existed)</t>
+          <t>No, initially -- deferred to Phase 5, built only if 30-day production measurement (Phase 4) shows call volume/latency/error evidence that justifies it. Client is designed so a cache can be inserted later without changing callers.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>PORTFOLIO -- one cache serving TI + Corralio + (later) RI, by design</t>
+          <t>One shared server module/client used by TI + Corralio (+ RI later) -- portfolio-wide at the INTEGRATION level from day one; response-data reuse across apps is deferred to Phase 5, not assumed from the start</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Weather forecast (daily + hourly) + severe weather alerts, replacing Open-Meteo</t>
+          <t>Weather forecast (daily + hourly) + severe weather alerts capability (unused), replacing Open-Meteo -- one shared client for TI + Corralio, Corralio shipped in the same build cycle (founder correction 2026-09-02)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>See rationale field.</t>
+          <t>REVISED 2026-09-02: see rationale field. Register updated in place per this session convention.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
